--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,21 @@
           <t>PnL_R$</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Lucro_Green_R$</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -615,6 +630,9 @@
       <c r="T2" t="n">
         <v>19.39</v>
       </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -700,6 +718,88 @@
       </c>
       <c r="T3" t="n">
         <v>16.97</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>COLOMBIA 1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>America De Cali x Alianza</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Match Odds (Away)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="M4" t="n">
+        <v>100</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3x0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -731,29 +731,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>ITALY CUP</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>America De Cali x Alianza</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>Cagliari x Verona</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -762,20 +770,20 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="K4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>7.41</v>
+        <v>8.33</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -787,20 +795,275 @@
         <v>1</v>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8.039999999999999</v>
+      </c>
       <c r="U4" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>COLOMBIA 1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>America De Cali x Alianza</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Match Odds (Away)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="M5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3x0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
         <v>7.15</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V5" t="n">
         <v>1</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>LIQUIDADO</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ECUADOR 1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CD Leones del Norte x Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CD Leones del Norte</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>30</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>200</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Nautico PE x Botafogo SP</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>29</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="M7" t="n">
+        <v>200</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-03.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -951,19 +951,19 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1038,19 +1038,19 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S7" t="n">
